--- a/template.xlsx
+++ b/template.xlsx
@@ -486,12 +486,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>時間碼 *</t>
+          <t>時間碼</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>可看點備註</t>
+          <t>說明</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -18572,7 +18572,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="時間碼" prompt="輸入 1:23、01:02:03、83（秒）或 1m23s" type="textLength" operator="lessThanOrEqual">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="時間碼" prompt="可不填。輸入 1:23、01:02:03、83（秒）或 1m23s" type="textLength" operator="lessThanOrEqual">
       <formula1>2000</formula1>
     </dataValidation>
   </dataValidations>
@@ -18662,24 +18662,24 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>時間碼 *</t>
+          <t>時間碼</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>必填。可寫 1:23、01:02:03、83（秒）或 1m23s。這一欄已設成「文字」格式，請不要改成時間格式，否則 1:23 會被 Excel 當成 1 小時 23 分。</t>
+          <t>選填。可寫 1:23、01:02:03、83（秒）或 1m23s；不填代表整部影片的說明。這一欄已設成「文字」格式，請不要改成時間格式，否則 1:23 會被 Excel 當成 1 小時 23 分。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>可看點備註</t>
+          <t>說明</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>選填。這個時間點的說明，最多 2000 字。</t>
+          <t>選填，最多 2000 字。時間碼和說明至少要填一個。</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>同一部影片、同一個時間碼、同樣備註的時間點如果已經存在，會自動略過，重複匯入同一個檔案也不會產生重複資料。</t>
+          <t>同一部影片、同一個時間碼、同樣說明的時間點如果已經存在，會自動略過，重複匯入同一個檔案也不會產生重複資料。</t>
         </is>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -18679,7 +18679,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>選填，最多 2000 字。時間碼和說明至少要填一個。</t>
+          <t>選填，最多 2000 字。時間碼和說明都不填時，只會建立影片，並自動加上「#待補」標籤。</t>
         </is>
       </c>
     </row>
